--- a/Supporting files/Reserves.xlsx
+++ b/Supporting files/Reserves.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Aluminium" sheetId="1" state="visible" r:id="rId2"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="147">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -74,361 +74,394 @@
     <t xml:space="preserve">China</t>
   </si>
   <si>
+    <t xml:space="preserve">Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vietnam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other countries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World total (rounded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolivia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyrgyzstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mexico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pakistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tajikistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World total (rounded, &gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">﻿World total (rounded)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zimbabwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Democratic Republic of the Congo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madagascar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papua New Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zambia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burkina Faso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanzania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzbekistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mozambique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sri Lanka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauritania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namibia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Greece</t>
   </si>
   <si>
-    <t xml:space="preserve">Guinea</t>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mongolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Caledonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Togo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tunisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thailand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Leone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afghanistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azerbaijan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bangladesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belarus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brunei Darussalam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameroon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czech Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equatorial Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guatemala</t>
   </si>
   <si>
     <t xml:space="preserve">Guyana</t>
   </si>
   <si>
-    <t xml:space="preserve">India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indonesia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamaica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Russia</t>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iraq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivory Coast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuwait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myanmar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Zealand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nigeria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of the Congo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Sudan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudan</t>
   </si>
   <si>
     <t xml:space="preserve">Suriname</t>
   </si>
   <si>
+    <t xml:space="preserve">Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timor-Leste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkmenistan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uganda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Arab Emirates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Kingdom</t>
+  </si>
+  <si>
     <t xml:space="preserve">Venezuela</t>
   </si>
   <si>
-    <t xml:space="preserve">Vietnam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other countries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World total (rounded)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bolivia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tajikistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mexico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">﻿World total (rounded)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World total (rounded, &gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Democratic Republic of the Congo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Caledonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zambia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papua New Guinea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uzbekistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madagascar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ukraine</t>
+    <t xml:space="preserve">Yemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethiopia</t>
   </si>
   <si>
     <t xml:space="preserve">Ireland</t>
   </si>
   <si>
-    <t xml:space="preserve">Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portugal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zimbabwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyrgyzstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mongolia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominican Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iraq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morocco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saudi Arabia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senegal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Togo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tunisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malaysia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mozambique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azerbaijan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bahrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bangladesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belarus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brunei Darussalam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameroon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equatorial Guinea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethiopia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guatemala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivory Coast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuwait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Libya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lithuania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mauritania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myanmar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netherlands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Zealand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nigeria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pakistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qatar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of the Congo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sierra Leone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Sudan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sudan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thailand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trinidad and Tobago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkmenistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uganda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Arab Emirates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yemen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afghanistan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namibia</t>
+    <t xml:space="preserve">Rwanda</t>
   </si>
   <si>
     <t xml:space="preserve">Slovenia</t>
@@ -437,25 +470,7 @@
     <t xml:space="preserve">Somalia</t>
   </si>
   <si>
-    <t xml:space="preserve">South Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanzania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timor-Leste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Bank and Gaza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botswana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Eswatini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greenland</t>
   </si>
   <si>
     <t xml:space="preserve">Laos</t>
@@ -489,7 +504,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -516,14 +531,6 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -569,7 +576,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -583,10 +590,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -607,7 +610,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -623,7 +626,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>20000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -631,7 +634,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>6500000</v>
+        <v>3500000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -639,7 +642,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>2600000</v>
+        <v>2700000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -647,7 +650,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>830000</v>
+        <v>680000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -655,7 +658,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>600000</v>
+        <v>7400000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -663,7 +666,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>7400000</v>
+        <v>650000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -671,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>850000</v>
+        <v>2800000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -679,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>540000</v>
+        <v>2000000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -687,7 +690,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1000000</v>
+        <v>280000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -695,7 +698,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>2000000</v>
+        <v>480000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -703,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>160000</v>
+        <v>180000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -711,7 +714,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>200000</v>
+        <v>69000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,7 +722,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>580000</v>
+        <v>3100000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -727,7 +730,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>320000</v>
+        <v>5300000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -735,23 +738,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>2100000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>28000000</v>
+        <v>29000000000</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +778,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>560</v>
@@ -807,7 +794,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>580</v>
@@ -815,7 +802,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>250</v>
@@ -823,7 +810,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">SUM(B2:B6)</f>
@@ -846,7 +833,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -862,7 +849,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>6900</v>
+        <v>3600000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -870,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>55700</v>
+        <v>58000000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -878,95 +865,135 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>31000</v>
+        <v>34000000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>6300</v>
+        <v>6000000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>8100</v>
+        <v>20000000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>2500</v>
+        <v>5500000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>2500</v>
+        <v>3800000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>25000</v>
+        <v>2500000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>6500</v>
+        <v>2600000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>18000</v>
+        <v>35000000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>190000</v>
+        <v>930000000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1300000000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>6500000000</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>17000000000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>200000000000</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +1012,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1001,7 +1028,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>5000</v>
+        <v>4600000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1009,111 +1036,103 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>35000</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1600</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>247</v>
+        <v>22000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>14000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>2600</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>600</v>
+        <v>5600000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>5600</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>7000</v>
+        <v>8900000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1700</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>9200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>300</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1100</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>87000</v>
+        <v>96000000</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1151,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1148,15 +1167,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>38000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>850000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1164,7 +1183,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1172,47 +1191,71 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>48000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>7500000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3500000</v>
+        <v>9300000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>60000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>23000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>13500000</v>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>30000000</v>
       </c>
     </row>
   </sheetData>
@@ -1247,7 +1290,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>10000</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1255,15 +1298,15 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>95000</v>
+        <v>280000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>15000</v>
+        <v>49000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1271,7 +1314,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>86000</v>
+        <v>200000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1279,79 +1322,79 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>500000</v>
+        <v>680000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>80000</v>
+        <v>280000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>20000</v>
+        <v>66000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>450000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>650000</v>
+        <v>2300000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>35000</v>
+        <v>1200000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>10000</v>
+        <v>35000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>49000</v>
+        <v>110000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>390000</v>
+        <v>2500000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>2400000</v>
+        <v>7700000000</v>
       </c>
     </row>
   </sheetData>
@@ -1370,7 +1413,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1383,90 +1426,66 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0</v>
+        <v>500000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>97000</v>
+        <v>270000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>54000</v>
+        <v>280000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>44000</v>
+        <v>61000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>24000</v>
+        <v>13000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>52000</v>
+        <v>34000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>5000</v>
+        <v>560000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>570000</v>
+        <v>1700000000</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +1504,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1501,12 +1520,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>2700000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>150000</v>
@@ -1517,23 +1536,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>200000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>260000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1800000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1541,36 +1560,36 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>4300000</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>50000</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>130000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>100000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>130000</v>
@@ -1578,50 +1597,42 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>160000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>450000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>250000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>100000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>11000000</v>
+        <v>15000000</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1651,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1656,7 +1667,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>160000</v>
+        <v>310000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1664,7 +1675,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>19000000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1672,15 +1683,15 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>9100000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>2900000</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1688,95 +1699,55 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>3000000</v>
+        <v>4400000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1100000</v>
+        <v>55000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>5500000</v>
+        <v>7100000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>930000</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>4500000</v>
+        <v>8300000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1600000</v>
+        <v>9100000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>12000000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>3100000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>7900000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>3700000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>6500000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>81000000</v>
+        <v>130000000</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1782,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1819,23 +1790,23 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>4100000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>4300000</v>
+        <v>17000000</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1825,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1870,15 +1841,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1100000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>2200000</v>
+        <v>2200000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1886,7 +1857,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1030000</v>
+        <v>1100000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1894,175 +1865,183 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>270000</v>
+        <v>1600000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>76000</v>
+        <v>3700000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3700000</v>
+        <v>2800000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>715000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>35000</v>
+        <v>31000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>430000</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>130000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>1300000</v>
+        <v>260000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>260000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>30000</v>
+        <v>50000000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>50000000</v>
+        <v>210000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>820000</v>
+        <v>2400000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>1300000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>211000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>50000</v>
+        <v>1500000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>1500000</v>
+        <v>250000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>1800000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>30000</v>
+        <v>2500000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>100000</v>
+        <v>71000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>30000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>300000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>67000000</v>
+        <v>800000000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>74000000000</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2060,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2094,58 +2073,114 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>310000</v>
+        <v>860000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>950000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>350000</v>
+        <v>310000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>27000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>50000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>150000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1800000</v>
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2000000</v>
       </c>
     </row>
   </sheetData>
@@ -2180,12 +2215,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>310</v>
@@ -2193,15 +2228,15 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1100</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>63000</v>
@@ -2209,18 +2244,18 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>66000</v>
+        <v>81000</v>
       </c>
     </row>
   </sheetData>
@@ -2239,7 +2274,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2255,7 +2290,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2263,7 +2298,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>63200000</v>
+        <v>5700000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2271,47 +2306,87 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>22000000</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>55000000</v>
+        <v>830000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>3100000</v>
+        <v>44000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>30000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>41000000</v>
+        <v>6900000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>130000000</v>
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>860000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>890000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>90000000</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2405,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2351,66 +2426,82 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>26000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>13000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>20000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>21000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>120000</v>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>92000</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2520,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2445,87 +2536,111 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>25000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>85000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>22000</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>7000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>77000</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>43000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>37000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>98900</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>85000</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>50000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>530000</v>
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>640000</v>
       </c>
     </row>
   </sheetData>
@@ -2544,7 +2659,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,7 +2675,15 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>6800000</v>
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>7100000</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2702,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2592,34 +2715,26 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>67000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>100000</v>
+        <v>240000</v>
       </c>
     </row>
   </sheetData>
@@ -2638,7 +2753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2654,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>2000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2662,103 +2777,87 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>198000</v>
+        <v>215000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>43000</v>
+        <v>51000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>31000</v>
+        <v>110000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>200000</v>
+        <v>15670000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>92400</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>40000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>14000</v>
+        <v>37000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>37000</v>
+        <v>34100000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>71300</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>8400</v>
+        <v>54540000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>26400</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>770000</v>
+        <v>560000000</v>
       </c>
     </row>
   </sheetData>
@@ -2777,7 +2876,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2790,90 +2889,82 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>140000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>160000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>10000</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>53000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>290000</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1900000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>4200</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>250000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>87000</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>3300000</v>
+        <v>4600000</v>
       </c>
     </row>
   </sheetData>
@@ -2892,7 +2983,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2916,39 +3007,47 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1800000</v>
+        <v>8500000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>5100000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>5000000</v>
+        <v>4100000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>15000000</v>
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>18000000</v>
       </c>
     </row>
   </sheetData>
@@ -2983,7 +3082,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>10000</v>
+        <v>9200000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2991,87 +3090,87 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>62000</v>
+        <v>64000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>4500</v>
+        <v>46000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>5900</v>
+        <v>9800000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>43000</v>
+        <v>7600000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>11000</v>
+        <v>14000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1100</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>10000</v>
+        <v>29000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>16000</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>29000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>42000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>230000</v>
+        <v>230000000</v>
       </c>
     </row>
   </sheetData>
@@ -3090,8 +3189,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3103,7 +3202,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>10000</v>
@@ -3111,7 +3210,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>5000</v>
@@ -3127,7 +3226,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>10000</v>
@@ -3135,27 +3234,35 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>50000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>320000</v>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>368000</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3165,7 +3272,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3181,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>500</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3189,7 +3296,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>51000</v>
+        <v>55000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3197,47 +3304,71 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>500</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>3400</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1100</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>14000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7200</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>78000</v>
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>5300000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>5700000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>70000000</v>
       </c>
     </row>
   </sheetData>
@@ -3256,7 +3387,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -3273,103 +3404,103 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>26000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1660000000</v>
+        <v>27000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1723000000</v>
+        <v>1660000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>317000000</v>
+        <v>347000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>542000000</v>
+        <v>386000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>7000000</v>
+        <v>202000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>952000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>15000000</v>
+        <v>952000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>4000000</v>
+        <v>23000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>27000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0</v>
+        <v>27000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>1000000</v>
@@ -3377,471 +3508,471 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>22000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>2202000000</v>
+        <v>33000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>150000000</v>
+        <v>2021000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>2000000</v>
+        <v>150000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>18000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>27065000000</v>
+        <v>27000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>204000000</v>
+        <v>25958000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>20000000</v>
+        <v>204000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>2514000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>314000000</v>
+        <v>3690000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>7000000</v>
+        <v>278000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>2000000</v>
+        <v>17000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>24000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>83000000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>1126000000</v>
+        <v>46000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>599000000</v>
+        <v>1126000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B32" s="0" t="n">
+        <v>449000000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="0" t="n">
         <v>150000000</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>11000000</v>
+        <v>172000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>272000000</v>
+        <v>11000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>5000000</v>
+        <v>272000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>31000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>90000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>1000000</v>
+        <v>90000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>11000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>4000000</v>
+        <v>11000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="0" t="n">
-        <v>740000000</v>
+      <c r="A42" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1497000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>502000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>21433000000</v>
+        <v>595000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>19465000000</v>
+        <v>309000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>2000000</v>
+        <v>28380000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>85000000</v>
+        <v>19730000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>14000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>4000000</v>
+        <v>79000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>0</v>
+        <v>14000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>4082000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>13810000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>5000000</v>
+        <v>4081000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>6580000000</v>
+        <v>13810000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>499000000</v>
+        <v>6580000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>1339000000</v>
+        <v>490000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>35000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>0</v>
+        <v>756000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>2000000</v>
+        <v>43000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>30000000</v>
+        <v>19000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>17000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>20000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>5044000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>880000000</v>
+        <v>5030000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>701000000</v>
+        <v>934000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>50000000</v>
+        <v>731000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>24000000</v>
+        <v>73000000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>183000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>15000000</v>
+        <v>117000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>19000000</v>
@@ -3849,250 +3980,266 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>3435000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>190000000</v>
+        <v>3435000000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>82000000</v>
+        <v>246000000</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>13187000000</v>
+        <v>82000000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>35524000000</v>
+        <v>14767000000</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>7000000</v>
+        <v>38891000000</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="B80" s="0" t="n">
-        <v>60000000</v>
+      <c r="A80" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>31000000</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>1000000</v>
+        <v>11000000</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>633000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>19000000</v>
+        <v>517000000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>200000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>12000000</v>
+        <v>177000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>340000000</v>
+        <v>13000000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>0</v>
+        <v>340000000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>53000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>113000000</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>58000000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>46000000</v>
+        <v>33000000</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>178000000</v>
+        <v>58000000</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>6857000000</v>
+        <v>50000000</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>136000000</v>
+        <v>82000000</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>54000000</v>
+        <v>8561000000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>13306000000</v>
+        <v>340000000</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>716000000</v>
+        <v>54000000</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>81000000</v>
+        <v>15374000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>26807000000</v>
+        <v>237000000</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>599000000</v>
+        <v>81000000</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>317000000</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B104" s="2" t="n">
-        <v>218806000000</v>
+        <v>47385000000</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>599000000</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B105" s="0" t="n">
+        <v>408000000</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>253647000000</v>
       </c>
     </row>
   </sheetData>
@@ -4111,7 +4258,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -4126,44 +4273,44 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="0" t="n">
         <v>40000000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1600000000</v>
+        <v>4800000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>3603200000000</v>
+        <v>1823200000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>220000000000</v>
+        <v>240800000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>262400000000</v>
+        <v>332800000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4171,52 +4318,52 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>2990400000000</v>
+        <v>1452000000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>8800000000</v>
+        <v>4000000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>932800000000</v>
+        <v>1533600000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>144800000000</v>
+        <v>54400000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>202400000000</v>
+        <v>56000000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>1600000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>2400000000</v>
@@ -4224,7 +4371,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>800000000</v>
@@ -4232,10 +4379,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>236800000000</v>
+        <v>170400000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4243,28 +4390,28 @@
         <v>4</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>371200000000</v>
+        <v>325600000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>216000000000</v>
+        <v>182400000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>4000000000</v>
+        <v>4800000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>108000000000</v>
@@ -4272,18 +4419,18 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>1624000000000</v>
+        <v>1971200000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>32000000000</v>
+        <v>78400000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4291,28 +4438,28 @@
         <v>5</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>2767200000000</v>
+        <v>5071200000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>124800000000</v>
+        <v>72000000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>17600000000</v>
+        <v>20000000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>56800000000</v>
@@ -4320,7 +4467,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>3200000000</v>
@@ -4328,7 +4475,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>800000000</v>
@@ -4336,55 +4483,55 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>28000000000</v>
+        <v>22400000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>4800000000</v>
+        <v>8800000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>1733600000000</v>
+        <v>1427200000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>87200000000</v>
+        <v>31200000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>4000000000</v>
+        <v>20000000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>7200000000</v>
+        <v>6400000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>20800000000</v>
@@ -4392,7 +4539,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>6400000000</v>
@@ -4400,15 +4547,15 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>71200000000</v>
+        <v>16000000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>18400000000</v>
@@ -4416,7 +4563,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>800000000</v>
@@ -4424,47 +4571,47 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>8000000000</v>
+        <v>3200000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>1141600000000</v>
+        <v>520000000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>2326400000000</v>
+        <v>823200000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>27216000000000</v>
+        <v>27190400000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>2870400000000</v>
+        <v>2971200000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>8000000000</v>
@@ -4472,31 +4619,31 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>179200000000</v>
+        <v>736000000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>39200000000</v>
+        <v>32000000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>12800000000</v>
+        <v>22400000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>16800000000</v>
@@ -4504,23 +4651,23 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>4800000000</v>
+        <v>3200000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>1543200000000</v>
+        <v>1464000000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>1427200000000</v>
@@ -4528,231 +4675,231 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>1204800000000</v>
+      <c r="A53" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1204000000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>1600000000</v>
+      <c r="A54" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1721600000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>1880800000000</v>
+      <c r="A55" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>224000000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>22400000000</v>
+        <v>249600000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>277600000000</v>
+        <v>4800000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>800000000</v>
+        <v>2265600000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>101600000000</v>
+        <v>509600000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>226400000000</v>
+        <v>49600000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>49600000000</v>
+        <v>74400000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>654400000000</v>
+        <v>29600000000</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>29600000000</v>
+        <v>4730400000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>4080000000000</v>
+        <v>1175200000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>1537600000000</v>
+        <v>520800000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>564000000000</v>
+        <v>473600000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>560000000000</v>
+        <v>136000000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>120800000000</v>
+        <v>240000000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>331200000000</v>
+        <v>79200000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>64000000000</v>
+        <v>74400000000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>68000000000</v>
+        <v>19064800000000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>19622400000000</v>
+        <v>227200000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>92000000000</v>
+        <v>84000000000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>88000000000</v>
+        <v>38207200000000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>38214400000000</v>
+      <c r="A75" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>45600000000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>6533600000000</v>
+      <c r="A76" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>7454400000000</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B77" s="3" t="n">
-        <v>1600000000</v>
+        <v>169600000000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B78" s="3" t="n">
-        <v>16000000000</v>
+        <v>38400000000</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B79" s="3" t="n">
-        <v>3200000000</v>
+        <v>11200000000</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B80" s="3" t="n">
         <v>800000000</v>
@@ -4760,7 +4907,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B81" s="3" t="n">
         <v>4800000000</v>
@@ -4768,23 +4915,23 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B82" s="3" t="n">
-        <v>6400000000</v>
+        <v>8000000000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="B83" s="3" t="n">
-        <v>800000000</v>
+        <v>5600000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B84" s="3" t="n">
         <v>2400000000</v>
@@ -4792,7 +4939,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B85" s="3" t="n">
         <v>68000000000</v>
@@ -4800,47 +4947,47 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B86" s="3" t="n">
-        <v>228000000000</v>
+        <v>192800000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>2400000000</v>
+      <c r="A87" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="0" t="n">
+        <v>4800000000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" s="3" t="n">
+      <c r="A88" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B88" s="0" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>29600000000</v>
+      <c r="A89" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B89" s="0" t="n">
+        <v>5600000000</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>190400000000</v>
+      <c r="A90" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B90" s="0" t="n">
+        <v>78400000000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>70400000000</v>
@@ -4848,15 +4995,15 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>277600000000</v>
+        <v>242400000000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B93" s="0" t="n">
         <v>52000000000</v>
@@ -4864,18 +5011,18 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>4800000000</v>
+        <v>2400000000</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>7947200000000</v>
+        <v>11160000000000</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4883,87 +5030,79 @@
         <v>2</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>7815200000000</v>
+        <v>13115200000000</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>4000000000</v>
+        <v>11200000000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B98" s="3" t="n">
-        <v>761600000000</v>
+        <v>883200000000</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B99" s="3" t="n">
-        <v>4872800000000</v>
+        <v>6560800000000</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>325600000000</v>
+      <c r="A100" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>116800000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>1305600000000</v>
+      <c r="A101" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101" s="0" t="n">
+        <v>1476800000000</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>4464800000000</v>
+      <c r="A102" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B102" s="0" t="n">
+        <v>4433600000000</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" s="0" t="n">
+        <v>488000000000</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B104" s="0" t="n">
+        <v>212800000000</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B103" s="3" t="n">
-        <v>493600000000</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>24000000000</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>215200000000</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B106" s="2" t="n">
-        <v>158273600000000</v>
+      <c r="B105" s="2" t="n">
+        <v>168676800000000</v>
       </c>
     </row>
   </sheetData>
@@ -4982,7 +5121,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -4999,7 +5138,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>66000000</v>
@@ -5007,7 +5146,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>59000000</v>
@@ -5015,7 +5154,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>500000000</v>
@@ -5023,7 +5162,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>163000000</v>
@@ -5034,12 +5173,12 @@
         <v>3</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>62095000000</v>
+        <v>75433000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>293000000</v>
@@ -5047,7 +5186,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>1000000</v>
@@ -5055,522 +5194,506 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>40000000</v>
+        <v>1547000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1547000000</v>
+        <v>192000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>192000000</v>
+        <v>4346000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>4346000000</v>
+        <v>1181000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>1181000000</v>
+        <v>146347000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>124059000000</v>
+        <v>4554000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>4881000000</v>
+        <v>1050000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>1107000000</v>
+        <v>88000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>88000000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>16000000</v>
+        <v>144000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>144000000</v>
+        <v>201000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>201000000</v>
+        <v>183000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>21000000</v>
+      <c r="A21" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>276000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>183000000</v>
+        <v>122253000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>276000000</v>
+        <v>21734000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>85562000000</v>
+        <v>1203000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>17394000000</v>
+        <v>14000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>1203000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>14000000</v>
+        <v>340000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>10000000</v>
+        <v>25605000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>340000000</v>
+        <v>971000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>25605000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>971000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>4000000</v>
+        <v>148000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>2000000</v>
+        <v>1160000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>141000000</v>
+        <v>1170000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>1160000000</v>
+        <v>142000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>1170000000</v>
+        <v>14000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>142000000</v>
+        <v>1792000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>14000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>1792000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>3000000</v>
+        <v>497000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>497000000</v>
+        <v>825000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>2000000</v>
+        <v>287000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>825000000</v>
+        <v>600000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>287000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>600000000</v>
+        <v>207000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>2000000</v>
+        <v>102000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>207000000</v>
+        <v>262000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>102000000</v>
+        <v>22687000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>211000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>16203000000</v>
+        <v>11000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>3000000</v>
+        <v>71719000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>11000000</v>
+        <v>402000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>69634000000</v>
+        <v>56000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>402000000</v>
+        <v>9893000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>56000000</v>
+        <v>326000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>9893000000</v>
+        <v>868000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>326000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>868000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>1000000</v>
+        <v>375000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>1000000</v>
+        <v>269000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>375000000</v>
+        <v>550000000</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>128</v>
+        <v>2</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>269000000</v>
+        <v>218016000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>380000000</v>
+        <v>32039000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>222641000000</v>
+        <v>28000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>32039000000</v>
+        <v>1375000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>70000000</v>
+        <v>731000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>1375000000</v>
+        <v>3116000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>731000000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>502000000</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="0" t="n">
-        <v>3116000000</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>45000000</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>502000000</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>698661000000</v>
+      <c r="B71" s="2" t="n">
+        <v>779003000000</v>
       </c>
     </row>
   </sheetData>
@@ -5589,7 +5712,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -5606,7 +5729,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>522000000</v>
@@ -5617,12 +5740,12 @@
         <v>3</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>44164000000</v>
+        <v>74039000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2264000000</v>
@@ -5638,7 +5761,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2174000000</v>
@@ -5646,7 +5769,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2236000000</v>
@@ -5654,7 +5777,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3000000</v>
@@ -5665,20 +5788,20 @@
         <v>5</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>7555000000</v>
+        <v>10694000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>2604000000</v>
+        <v>2408000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>24000000</v>
@@ -5686,15 +5809,15 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>36300000000</v>
+        <v>35400000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>2876000000</v>
@@ -5702,7 +5825,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>2633000000</v>
@@ -5710,23 +5833,23 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>4714000000</v>
+        <v>5474000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>8274000000</v>
+        <v>13321000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>7000000</v>
@@ -5734,7 +5857,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>10000000</v>
@@ -5742,7 +5865,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>1564000000</v>
@@ -5750,7 +5873,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>499000000</v>
@@ -5758,15 +5881,15 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>39000000</v>
+        <v>78000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>51000000</v>
@@ -5774,7 +5897,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>1350000000</v>
@@ -5782,7 +5905,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>3000000</v>
@@ -5790,7 +5913,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>6750000000</v>
@@ -5798,7 +5921,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>6000000</v>
@@ -5806,7 +5929,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>57000000</v>
@@ -5814,7 +5937,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>332000000</v>
@@ -5822,7 +5945,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>2857000000</v>
@@ -5830,23 +5953,23 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>105000000</v>
+        <v>147000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>5429000000</v>
+        <v>5071000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>33000000</v>
@@ -5854,7 +5977,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>280000000</v>
@@ -5862,15 +5985,15 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>90730000000</v>
+        <v>90447000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>7112000000</v>
@@ -5878,7 +6001,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>135000000</v>
@@ -5886,7 +6009,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>315000000</v>
@@ -5894,7 +6017,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>319000000</v>
@@ -5902,7 +6025,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1063000000</v>
@@ -5910,10 +6033,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>12466000000</v>
+        <v>10975000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,12 +6044,12 @@
         <v>2</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>30483000000</v>
+        <v>29867000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>2336000000</v>
@@ -5934,7 +6057,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>244000000</v>
@@ -5942,15 +6065,11 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>285967000000</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
+        <v>321025000000</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5968,7 +6087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -5985,10 +6104,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5996,15 +6115,15 @@
         <v>4</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>155000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>275000</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6012,12 +6131,12 @@
         <v>5</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>94000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2000</v>
@@ -6025,7 +6144,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>5000</v>
@@ -6033,121 +6152,129 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>236000</v>
+        <v>316000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>108000</v>
+      <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="B10" s="3" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>1000</v>
-      </c>
-    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>5000</v>
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>14000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>12000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>9000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>113000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>38000</v>
+        <v>166000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>7000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>39000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>50000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="2" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2" t="n">
         <v>1213000</v>
       </c>
     </row>
@@ -6188,7 +6315,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>23000</v>
@@ -6204,7 +6331,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>35000</v>
@@ -6212,7 +6339,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>30000</v>
@@ -6220,7 +6347,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>47000</v>
@@ -6228,7 +6355,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>55000</v>
@@ -6236,7 +6363,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>16000</v>
@@ -6244,7 +6371,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>44000</v>
@@ -6252,7 +6379,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>130000</v>
@@ -6260,7 +6387,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>500000</v>
@@ -6282,7 +6409,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6298,39 +6425,71 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>620</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>54000</v>
+        <v>6600000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>230000</v>
+        <v>8300000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>200000</v>
+        <v>79000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>480000</v>
+        <v>320000000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>200000000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>27000000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>540000000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1200000000</v>
       </c>
     </row>
   </sheetData>
@@ -6349,7 +6508,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6365,7 +6524,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>37000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6373,68 +6532,68 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1100000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>85000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>250000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>80000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3400000</v>
+        <v>640000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>200000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>270000</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>250000</v>
@@ -6442,34 +6601,26 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>32000</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>270000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>7200000</v>
+        <v>11000000</v>
       </c>
     </row>
   </sheetData>
@@ -6488,7 +6639,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6504,7 +6655,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>35000</v>
+        <v>47000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6512,23 +6663,23 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>93000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>11000</v>
+        <v>8300000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>209000</v>
+        <v>190000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6536,87 +6687,95 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>30000</v>
+        <v>41000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>20000</v>
+        <v>80000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>25000</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>6000</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>38000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>68000</v>
+        <v>53000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>28000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>30000</v>
+        <v>34000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>20000</v>
+        <v>80000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>90000</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>700000</v>
+        <v>180000000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>980000000</v>
       </c>
     </row>
   </sheetData>
@@ -6635,7 +6794,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6659,7 +6818,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>9800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6672,18 +6831,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>3900</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6691,87 +6850,111 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1900</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1400</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>2100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>5000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>1700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>55000</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>64000</v>
       </c>
     </row>
   </sheetData>
@@ -6790,7 +6973,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6806,7 +6989,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>40000</v>
+        <v>74000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6814,39 +6997,111 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>55000</v>
+        <v>81000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>11000</v>
+        <v>8600000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>940</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>3100</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>110000</v>
+        <v>27000000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>3100000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>18000000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>6900000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>9700000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>290000000</v>
       </c>
     </row>
   </sheetData>

--- a/Supporting files/Reserves.xlsx
+++ b/Supporting files/Reserves.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="Aluminium" sheetId="1" state="visible" r:id="rId2"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="147">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -576,7 +576,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -586,10 +586,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -758,61 +754,61 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>560</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <f aca="false">SUM(B2:B6)</f>
         <v>11840</v>
       </c>
@@ -2659,7 +2655,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2684,6 +2680,14 @@
       </c>
       <c r="B3" s="1" t="n">
         <v>7100000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>19100000</v>
       </c>
     </row>
   </sheetData>
@@ -2702,7 +2706,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2735,6 +2739,14 @@
       </c>
       <c r="B4" s="1" t="n">
         <v>240000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>390000</v>
       </c>
     </row>
   </sheetData>
@@ -3388,10 +3400,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B106"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3403,834 +3415,834 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>12000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>27000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1660000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>347000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>386000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>202000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>5000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>952000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>23000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>27000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>2021000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>150000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>27000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>25958000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>204000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>3690000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>278000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>17000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>24000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>46000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>1126000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>449000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>150000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>172000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>272000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>5000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>15000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>90000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="1" t="n">
         <v>1497000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>595000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>309000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>28380000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>19730000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>79000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>4081000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>13810000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>5000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>6580000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>490000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>756000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>43000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>19000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>9000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>8000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>5030000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>934000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>731000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>73000000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="1" t="n">
         <v>117000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="1" t="n">
         <v>19000000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="1" t="n">
         <v>3435000000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="1" t="n">
         <v>246000000</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B77" s="0" t="n">
+      <c r="B77" s="1" t="n">
         <v>82000000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="0" t="n">
+      <c r="B78" s="1" t="n">
         <v>14767000000</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="1" t="n">
         <v>38891000000</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="1" t="n">
         <v>31000000</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B81" s="0" t="n">
+      <c r="B81" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B83" s="0" t="n">
+      <c r="B83" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B84" s="0" t="n">
+      <c r="B84" s="1" t="n">
         <v>517000000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="1" t="n">
         <v>20000000</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="1" t="n">
         <v>177000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="1" t="n">
         <v>13000000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="1" t="n">
         <v>340000000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="1" t="n">
         <v>21000000</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>25000000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="1" t="n">
         <v>58000000</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>50000000</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>82000000</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>8561000000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="1" t="n">
         <v>340000000</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" s="1" t="n">
         <v>54000000</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="1" t="n">
         <v>15374000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="1" t="n">
         <v>237000000</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="1" t="n">
         <v>81000000</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="1" t="n">
         <v>47385000000</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="1" t="n">
         <v>599000000</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="1" t="n">
         <v>408000000</v>
       </c>
     </row>
@@ -4259,10 +4271,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B105"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4274,826 +4286,826 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>40000000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1823200000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>240800000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>332800000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>1452000000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>4000000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>1533600000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>54400000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>56000000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>2400000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>170400000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>325600000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>182400000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>108000000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>1971200000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="1" t="n">
         <v>78400000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>5071200000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>72000000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>20000000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>56800000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>3200000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>22400000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>8800000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>1427200000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>31200000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>20000000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>6400000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>20800000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>6400000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>16000000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>18400000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>3200000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>520000000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>823200000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>27190400000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>2971200000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>8000000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>736000000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>32000000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>22400000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>16800000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>3200000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>1464000000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>1427200000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>1204000000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>1721600000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>224000000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>249600000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>2265600000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>509600000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>49600000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>74400000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>29600000000</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>4730400000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>1175200000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>520800000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>473600000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>136000000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>240000000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>79200000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>74400000000</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="1" t="n">
         <v>19064800000000</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="1" t="n">
         <v>227200000000</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="1" t="n">
         <v>84000000000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="1" t="n">
         <v>38207200000000</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="1" t="n">
         <v>45600000000</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="1" t="n">
         <v>7454400000000</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="1" t="n">
         <v>169600000000</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="1" t="n">
         <v>38400000000</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="1" t="n">
         <v>11200000000</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B80" s="3" t="n">
+      <c r="B80" s="1" t="n">
         <v>800000000</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B81" s="3" t="n">
+      <c r="B81" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B82" s="1" t="n">
         <v>8000000000</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B83" s="1" t="n">
         <v>5600000000</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B84" s="3" t="n">
+      <c r="B84" s="1" t="n">
         <v>2400000000</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B85" s="1" t="n">
         <v>68000000000</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B86" s="3" t="n">
+      <c r="B86" s="1" t="n">
         <v>192800000000</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="1" t="n">
         <v>4800000000</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="1" t="n">
         <v>5600000000</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="1" t="n">
         <v>78400000000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="1" t="n">
         <v>70400000000</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="1" t="n">
         <v>242400000000</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="1" t="n">
         <v>52000000000</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="1" t="n">
         <v>2400000000</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="1" t="n">
         <v>11160000000000</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="1" t="n">
         <v>13115200000000</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="1" t="n">
         <v>11200000000</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B98" s="1" t="n">
         <v>883200000000</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="1" t="n">
         <v>6560800000000</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="1" t="n">
         <v>116800000000</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="1" t="n">
         <v>1476800000000</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="1" t="n">
         <v>4433600000000</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="1" t="n">
         <v>488000000000</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="1" t="n">
         <v>212800000000</v>
       </c>
     </row>
@@ -5122,10 +5134,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B71"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5137,554 +5149,554 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>66000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>59000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>500000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>163000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>75433000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>293000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>1547000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>192000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>4346000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>1181000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>146347000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>4554000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>1050000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>88000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>16000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>144000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>201000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>183000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>276000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>122253000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>21734000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>1203000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>340000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>25605000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>971000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>4000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>148000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>1160000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>1170000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>142000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>14000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>1792000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>497000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>825000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>287000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="1" t="n">
         <v>600000000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="1" t="n">
         <v>2000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="1" t="n">
         <v>207000000</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="1" t="n">
         <v>102000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="1" t="n">
         <v>262000000</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="1" t="n">
         <v>22687000000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="1" t="n">
         <v>11000000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="1" t="n">
         <v>71719000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="1" t="n">
         <v>402000000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="1" t="n">
         <v>56000000</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="1" t="n">
         <v>9893000000</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="1" t="n">
         <v>326000000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="1" t="n">
         <v>868000000</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="1" t="n">
         <v>375000000</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="1" t="n">
         <v>269000000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="1" t="n">
         <v>550000000</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="1" t="n">
         <v>218016000000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="1" t="n">
         <v>32039000000</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="1" t="n">
         <v>28000000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="1" t="n">
         <v>1375000000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="1" t="n">
         <v>731000000</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="1" t="n">
         <v>3116000000</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="1" t="n">
         <v>45000000</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="1" t="n">
         <v>502000000</v>
       </c>
     </row>
@@ -5713,10 +5725,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5728,338 +5740,338 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>522000000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>74039000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>2264000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>5049000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2174000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>2236000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>10694000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>2408000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>24000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>35400000000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>2876000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>2633000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>5474000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>13321000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>7000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>10000000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>1564000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>499000000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>78000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>51000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>1350000000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>3000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>6750000000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>6000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>57000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>332000000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>2857000000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>147000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>5071000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>33000000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>280000000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>90447000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>7112000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>135000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>315000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="1" t="n">
         <v>319000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="1" t="n">
         <v>1063000000</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="1" t="n">
         <v>10975000000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="1" t="n">
         <v>29867000000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="1" t="n">
         <v>2336000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="1" t="n">
         <v>244000000</v>
       </c>
     </row>
@@ -6088,10 +6100,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6103,170 +6115,170 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>156000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>282000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>56000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>316000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="1" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="1" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="1" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="1" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>21000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>166000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>27000</v>
       </c>
     </row>
